--- a/artfynd/A 25441-2022 artfynd.xlsx
+++ b/artfynd/A 25441-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25441-2022 artfynd.xlsx
+++ b/artfynd/A 25441-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105614363</v>
+        <v>105613852</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -722,24 +716,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnvägen / Lenasväg, Benareby, Råda, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>330808.8863362081</v>
+        <v>330809</v>
       </c>
       <c r="R2" t="n">
-        <v>6392516.491294391</v>
+        <v>6392516</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -809,42 +788,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105613852</v>
+        <v>108950309</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -852,23 +826,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnvägen / Lenasväg, Benareby, Råda, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>330808.8863362081</v>
+        <v>330809</v>
       </c>
       <c r="R3" t="n">
-        <v>6392516.491294391</v>
+        <v>6392516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,22 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,37 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108950309</v>
+        <v>105614363</v>
       </c>
       <c r="B4" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,19 +937,21 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -996,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>330808.8863362081</v>
+        <v>330809</v>
       </c>
       <c r="R4" t="n">
-        <v>6392516.491294391</v>
+        <v>6392516</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,22 +990,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25441-2022 artfynd.xlsx
+++ b/artfynd/A 25441-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105613852</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108950309</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105614363</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>